--- a/assets/gantt_master_data_template.xlsx
+++ b/assets/gantt_master_data_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt Master Data" sheetId="1" r:id="R0bcc4ecac84d4537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R9da7878c329b4bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt Master Data" sheetId="1" r:id="R6badb0ee841047de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R67839cd19b1c440e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,45 +51,21 @@
   <x:borders count="12">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="61">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -222,6 +198,21 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1024,7 +1015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc828654ab5c54b65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd9a88cd36fb4724"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1082,7 +1073,7 @@
         <x:v>Frequency</x:v>
       </x:c>
       <x:c r="B6" s="58" t="str">
-        <x:v>Do not upload this field. IARS calculates it automatically from the number of Done audits for the custodian in the selected year.</x:v>
+        <x:v>Do not upload this field. IARS calculates it from Done audits for the exact Company / Department, Custodian, Audit Task, and Accountability record in the selected year.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -1098,7 +1089,7 @@
         <x:v>Upload behavior</x:v>
       </x:c>
       <x:c r="B8" s="58" t="str">
-        <x:v>Existing matching Company / Department + Custodian + Audit Task records are updated; new records are added.</x:v>
+        <x:v>Existing records are updated only when all four fields match: Company / Department, Custodian, Audit Task, and Accountability.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -1107,6 +1098,14 @@
       </x:c>
       <x:c r="B9" s="60" t="str">
         <x:v>Keep the four column headers exactly as shown in the Gantt Master Data sheet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="64" t="str">
+        <x:v>Duplicate rule</x:v>
+      </x:c>
+      <x:c r="B10" s="65" t="str">
+        <x:v>The same custodian may appear in multiple rows when the Audit Task or Accountability is different. Only an exact duplicate of all four fields is blocked.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
